--- a/config/yunying/oncerechage.xlsx
+++ b/config/yunying/oncerechage.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oncerechage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oncerechage" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>単発で6580ダイヤ購入</t>
+          <t>单独购买6580颗钻石</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>単発で3380ダイヤ購入</t>
+          <t>一次性购买3380颗钻石</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>単発で1980ダイヤ購入</t>
+          <t>单独购买1980颗钻石</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>単発で980ダイヤ購入</t>
+          <t>一次性购买980颗钻石</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>単発で580ダイヤ購入</t>
+          <t>一次性购买580颗钻石</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>単発で340ダイヤ購入</t>
+          <t>一次性购买340颗钻石</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>単発で66ダイヤ購入</t>
+          <t>单独购买66颗钻石</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1862,22 +1862,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1912,7 +1897,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>単発で6580ダイヤ購入</t>
+          <t>单独购买6580颗钻石</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1994,7 +1979,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>単発で3380ダイヤ購入</t>
+          <t>一次性购买3380颗钻石</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2076,7 +2061,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>単発で1980ダイヤ購入</t>
+          <t>单独购买1980颗钻石</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2158,7 +2143,7 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>単発で980ダイヤ購入</t>
+          <t>一次性购买980颗钻石</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2240,7 +2225,7 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>単発で580ダイヤ購入</t>
+          <t>一次性购买580颗钻石</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2322,7 +2307,7 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>単発で340ダイヤ購入</t>
+          <t>一次性购买340颗钻石</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2404,7 +2389,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>単発で66ダイヤ購入</t>
+          <t>单独购买66颗钻石</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2454,22 +2439,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2504,7 +2474,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>単発で6580ダイヤ購入</t>
+          <t>单独购买6580颗钻石</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2586,7 +2556,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>単発で3380ダイヤ購入</t>
+          <t>一次性购买3380颗钻石</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2668,7 +2638,7 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>単発で1980ダイヤ購入</t>
+          <t>单独购买1980颗钻石</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2750,7 +2720,7 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>単発で980ダイヤ購入</t>
+          <t>一次性购买980颗钻石</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2832,7 +2802,7 @@
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>単発で580ダイヤ購入</t>
+          <t>一次性购买580颗钻石</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2914,7 +2884,7 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>単発で340ダイヤ購入</t>
+          <t>一次性购买340颗钻石</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2996,7 +2966,7 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>単発で66ダイヤ購入</t>
+          <t>单独购买66颗钻石</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
